--- a/artfynd/A 41916-2026 artfynd.xlsx
+++ b/artfynd/A 41916-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128291346</v>
+        <v>137520690</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496634</v>
+        <v>496567</v>
       </c>
       <c r="R2" t="n">
-        <v>6773946</v>
+        <v>6773665</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Klen granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,24 +780,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291346</t>
+          <t>https://artportalen.se/Sighting/137520690</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128291347</v>
+        <v>128291346</v>
       </c>
       <c r="B3" t="n">
         <v>79327</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496603</v>
+        <v>496634</v>
       </c>
       <c r="R3" t="n">
-        <v>6773923</v>
+        <v>6773946</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,13 +903,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291347</t>
+          <t>https://artportalen.se/Sighting/128291346</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128291348</v>
+        <v>128291347</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496537</v>
+        <v>496603</v>
       </c>
       <c r="R4" t="n">
-        <v>6774034</v>
+        <v>6773923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,13 +1015,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291348</t>
+          <t>https://artportalen.se/Sighting/128291347</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128291349</v>
+        <v>128291348</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496580</v>
+        <v>496537</v>
       </c>
       <c r="R5" t="n">
-        <v>6774075</v>
+        <v>6774034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,51 +1127,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291349</t>
+          <t>https://artportalen.se/Sighting/128291348</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128240684</v>
+        <v>128291349</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kallåsen, Kallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496595</v>
+        <v>496580</v>
       </c>
       <c r="R6" t="n">
-        <v>6774129</v>
+        <v>6774075</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,27 +1198,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födohål, Färska</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,65 +1228,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128240684</t>
+          <t>https://artportalen.se/Sighting/128291349</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128240975</v>
+        <v>137520677</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>79536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kallåsen, Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496609</v>
+        <v>496559</v>
       </c>
       <c r="R7" t="n">
-        <v>6773939</v>
+        <v>6774101</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,27 +1310,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bohål. Bild finns</t>
+          <t>Gran, gammal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,65 +1345,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128240975</t>
+          <t>https://artportalen.se/Sighting/137520677</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291330</v>
+        <v>137520678</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496633</v>
+        <v>496562</v>
       </c>
       <c r="R8" t="n">
-        <v>6773937</v>
+        <v>6774093</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,22 +1427,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,65 +1462,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291330</t>
+          <t>https://artportalen.se/Sighting/137520678</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291324</v>
+        <v>137520680</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496609</v>
+        <v>496563</v>
       </c>
       <c r="R9" t="n">
-        <v>6773957</v>
+        <v>6774072</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,22 +1544,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,69 +1579,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291324</t>
+          <t>https://artportalen.se/Sighting/137520680</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291325</v>
+        <v>137520684</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496585</v>
+        <v>496557</v>
       </c>
       <c r="R10" t="n">
-        <v>6773946</v>
+        <v>6774010</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1655,22 +1661,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,73 +1696,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291325</t>
+          <t>https://artportalen.se/Sighting/137520684</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291335</v>
+        <v>137520686</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496607</v>
+        <v>496590</v>
       </c>
       <c r="R11" t="n">
-        <v>6773883</v>
+        <v>6773910</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,22 +1778,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,18 +1813,1531 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137520686</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137520687</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496599</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6773912</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520687</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137520688</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496625</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6773910</v>
+      </c>
+      <c r="S13" t="n">
+        <v>17</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran, rikligt med lågor, även grov gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520688</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137520689</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496625</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6773924</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520689</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128240684</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kallåsen, Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496595</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6774129</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födohål, Färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128240684</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128240975</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kallåsen, Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496609</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6773939</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bohål. Bild finns</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128240975</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128291330</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496633</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6773937</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291330</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128291324</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496609</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6773957</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291324</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128291325</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496585</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6773946</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291325</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128291335</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496607</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6773883</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128291335</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137520682</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496576</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6774040</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520682</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137520681</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496576</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6774040</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520681</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137520683</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496560</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6774022</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520683</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137520679</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99435</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496555</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6774067</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>0,5 m2</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520679</t>
         </is>
       </c>
     </row>
@@ -1832,6 +3353,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41916-2026 artfynd.xlsx
+++ b/artfynd/A 41916-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137520690</v>
       </c>
       <c r="B2" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,48 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128291346</v>
+        <v>137569225</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kallåsen, Dlr</t>
+          <t>KALLÅSEN, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496634</v>
+        <v>496611</v>
       </c>
       <c r="R3" t="n">
-        <v>6773946</v>
+        <v>6773904</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket gamla granlågor olika stadier bland nyröjda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,24 +897,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291346</t>
+          <t>https://artportalen.se/Sighting/137569225</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128291347</v>
+        <v>128291346</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496603</v>
+        <v>496634</v>
       </c>
       <c r="R4" t="n">
-        <v>6773923</v>
+        <v>6773946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,13 +1020,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291347</t>
+          <t>https://artportalen.se/Sighting/128291346</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128291348</v>
+        <v>128291347</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496537</v>
+        <v>496603</v>
       </c>
       <c r="R5" t="n">
-        <v>6774034</v>
+        <v>6773923</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,13 +1132,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291348</t>
+          <t>https://artportalen.se/Sighting/128291347</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291349</v>
+        <v>128291348</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496580</v>
+        <v>496537</v>
       </c>
       <c r="R6" t="n">
-        <v>6774075</v>
+        <v>6774034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,16 +1244,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291349</t>
+          <t>https://artportalen.se/Sighting/128291348</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137520677</v>
+        <v>128291349</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,17 +1281,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496559</v>
+        <v>496580</v>
       </c>
       <c r="R7" t="n">
-        <v>6774101</v>
+        <v>6774075</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,27 +1315,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gran, gammal</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,27 +1345,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520677</t>
+          <t>https://artportalen.se/Sighting/128291349</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137520678</v>
+        <v>137520677</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496562</v>
+        <v>496559</v>
       </c>
       <c r="R8" t="n">
-        <v>6774093</v>
+        <v>6774101</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran, gammal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,16 +1473,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520678</t>
+          <t>https://artportalen.se/Sighting/137520677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137520680</v>
+        <v>137520678</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496563</v>
+        <v>496562</v>
       </c>
       <c r="R9" t="n">
-        <v>6774072</v>
+        <v>6774093</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,16 +1590,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520680</t>
+          <t>https://artportalen.se/Sighting/137520678</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137520684</v>
+        <v>137520680</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496557</v>
+        <v>496563</v>
       </c>
       <c r="R10" t="n">
-        <v>6774010</v>
+        <v>6774072</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,16 +1707,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520684</t>
+          <t>https://artportalen.se/Sighting/137520680</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137520686</v>
+        <v>137520684</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496590</v>
+        <v>496557</v>
       </c>
       <c r="R11" t="n">
-        <v>6773910</v>
+        <v>6774010</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1824,16 +1824,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520686</t>
+          <t>https://artportalen.se/Sighting/137520684</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137520687</v>
+        <v>137520686</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496599</v>
+        <v>496590</v>
       </c>
       <c r="R12" t="n">
-        <v>6773912</v>
+        <v>6773910</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1941,16 +1941,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520687</t>
+          <t>https://artportalen.se/Sighting/137520686</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137520688</v>
+        <v>137520687</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496625</v>
+        <v>496599</v>
       </c>
       <c r="R13" t="n">
-        <v>6773910</v>
+        <v>6773912</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran, rikligt med lågor, även grov gammal tallåga</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,16 +2058,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520688</t>
+          <t>https://artportalen.se/Sighting/137520687</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137520689</v>
+        <v>137520688</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         <v>496625</v>
       </c>
       <c r="R14" t="n">
-        <v>6773924</v>
+        <v>6773910</v>
       </c>
       <c r="S14" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Torrgran</t>
+          <t>På gran, rikligt med lågor, även grov gammal tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,54 +2175,54 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520689</t>
+          <t>https://artportalen.se/Sighting/137520688</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128240684</v>
+        <v>137520689</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kallåsen, Kallåsen, Dlr</t>
+          <t>Tallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496595</v>
+        <v>496625</v>
       </c>
       <c r="R15" t="n">
-        <v>6774129</v>
+        <v>6773924</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2246,27 +2246,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Födohål, Färska</t>
+          <t>Torrgran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,65 +2281,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128240684</t>
+          <t>https://artportalen.se/Sighting/137520689</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128240975</v>
+        <v>137522663</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kallåsen, Kallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496609</v>
+        <v>496592</v>
       </c>
       <c r="R16" t="n">
-        <v>6773939</v>
+        <v>6774104</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2363,27 +2363,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Bohål. Bild finns</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,49 +2393,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128240975</t>
+          <t>https://artportalen.se/Sighting/137522663</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291330</v>
+        <v>137522664</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2450,13 +2445,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496633</v>
+        <v>496590</v>
       </c>
       <c r="R17" t="n">
-        <v>6773937</v>
+        <v>6774104</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2480,22 +2475,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,49 +2505,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291330</t>
+          <t>https://artportalen.se/Sighting/137522664</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291324</v>
+        <v>137522669</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2562,13 +2557,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496609</v>
+        <v>496557</v>
       </c>
       <c r="R18" t="n">
-        <v>6773957</v>
+        <v>6774084</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2592,22 +2587,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,69 +2617,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291324</t>
+          <t>https://artportalen.se/Sighting/137522669</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128291325</v>
+        <v>137522670</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496585</v>
+        <v>496529</v>
       </c>
       <c r="R19" t="n">
-        <v>6773946</v>
+        <v>6774093</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,22 +2699,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,73 +2729,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291325</t>
+          <t>https://artportalen.se/Sighting/137522670</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291335</v>
+        <v>137522672</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496607</v>
+        <v>496553</v>
       </c>
       <c r="R20" t="n">
-        <v>6773883</v>
+        <v>6774015</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,22 +2811,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,62 +2841,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128291335</t>
+          <t>https://artportalen.se/Sighting/137522672</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137520682</v>
+        <v>137522677</v>
       </c>
       <c r="B21" t="n">
-        <v>5188</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496576</v>
+        <v>496580</v>
       </c>
       <c r="R21" t="n">
-        <v>6774040</v>
+        <v>6773931</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2945,7 +2928,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,12 +2938,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Torrgran</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,62 +2953,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520682</t>
+          <t>https://artportalen.se/Sighting/137522677</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137520681</v>
+        <v>137522678</v>
       </c>
       <c r="B22" t="n">
-        <v>5208</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496576</v>
+        <v>496581</v>
       </c>
       <c r="R22" t="n">
-        <v>6774040</v>
+        <v>6773928</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3062,7 +3040,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,12 +3050,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Torrgran</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,65 +3065,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520681</t>
+          <t>https://artportalen.se/Sighting/137522678</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137520683</v>
+        <v>137522679</v>
       </c>
       <c r="B23" t="n">
-        <v>5208</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496560</v>
+        <v>496587</v>
       </c>
       <c r="R23" t="n">
-        <v>6774022</v>
+        <v>6773912</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3179,7 +3152,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3189,12 +3162,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Torrgran</t>
+          <t>Rikligt till måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,27 +3182,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137520683</t>
+          <t>https://artportalen.se/Sighting/137522679</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137520679</v>
+        <v>137522680</v>
       </c>
       <c r="B24" t="n">
-        <v>99435</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,37 +3210,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tallåsen, Dlr</t>
+          <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496555</v>
+        <v>496611</v>
       </c>
       <c r="R24" t="n">
-        <v>6774067</v>
+        <v>6773936</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3296,7 +3269,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,12 +3279,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0,5 m2</t>
+          <t>Rikligt till måttligt i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,16 +3299,4406 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522680</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137522681</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496617</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6773979</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522681</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137522682</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496632</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6773951</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522682</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137522684</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496633</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6773956</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522684</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137522685</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496634</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6773948</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 30 meter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522685</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137522687</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>496632</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6773931</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Med miljöbild</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522687</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137522688</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>496650</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6773838</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522688</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137522689</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>496673</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6773787</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522689</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137522690</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>496653</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6773755</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522690</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137522692</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>496624</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6773765</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522692</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137523382</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>496560</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6774048</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523382</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137523386</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>496607</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6773685</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttligt</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523386</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137569218</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>496505</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6774079</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569218</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137569221</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>496532</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6774033</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569221</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137569228</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>496647</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6773879</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På stor tall kammossa</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569228</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137569231</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>496651</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6773873</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569231</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137569235</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79539</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>496614</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6773715</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569235</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128240684</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kallåsen, Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>496595</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6774129</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Födohål, Färska</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128240684</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128240975</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kallåsen, Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>496609</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6773939</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bohål. Bild finns</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128240975</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128291330</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>496633</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6773937</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291330</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137522683</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>496633</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6773956</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522683</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137523381</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>496559</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6774084</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523381</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137569230</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>496648</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6773872</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569230</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128291324</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>496609</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6773957</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291324</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128291325</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>496585</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6773946</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291325</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128291335</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>496607</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6773883</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128291335</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137522667</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>496567</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6774072</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522667</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137522673</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>496557</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6774013</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522673</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137522686</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>496631</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6773929</v>
+      </c>
+      <c r="S52" t="n">
+        <v>12</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2 meter upp,  två bohål/hackhål, 4,5 och 5 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522686</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137523384</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>496602</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6773920</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523384</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137523385</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58038</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kallåsen Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>496644</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6773880</v>
+      </c>
+      <c r="S54" t="n">
+        <v>9</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack i tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137523385</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137522694</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57224</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>496648</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6773731</v>
+      </c>
+      <c r="S55" t="n">
+        <v>9</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137522694</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137570361</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57224</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>496532</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6774033</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Betad tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137570361</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137520682</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>496576</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6774040</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520682</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137520681</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>496576</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6774040</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520681</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137520683</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5208</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>496560</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6774022</v>
+      </c>
+      <c r="S59" t="n">
+        <v>14</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Torrgran</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137520683</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137569227</v>
+      </c>
+      <c r="B60" t="n">
+        <v>111438</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>496634</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6773887</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569227</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137569233</v>
+      </c>
+      <c r="B61" t="n">
+        <v>111438</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>KALLÅSEN, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>496642</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6773800</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137569233</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137520679</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99438</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tallåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>496555</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6774067</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>0,5 m2</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137520679</t>
         </is>
@@ -3366,6 +7729,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
